--- a/output/pdf_financials_xlsx/DFSC.xlsx
+++ b/output/pdf_financials_xlsx/DFSC.xlsx
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.040704</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.040704</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -13106,7 +13106,11 @@
           <t>Reserve (Note 4)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DFSC.xlsx
+++ b/output/pdf_financials_xlsx/DFSC.xlsx
@@ -1567,19 +1567,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.066759</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.20101</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.07376</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.688105</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.170545</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>5.407009</v>
@@ -1633,19 +1633,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.066759</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.20101</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.07376</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.688105</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.170545</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>5.407009</v>
@@ -2029,19 +2029,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.099884</v>
+        <v>0.033125</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.20101</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.515597</v>
+        <v>0.441837</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.266147</v>
+        <v>0.5780419999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.950973</v>
+        <v>0.780428</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.592408</v>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">

--- a/output/pdf_financials_xlsx/DFSC.xlsx
+++ b/output/pdf_financials_xlsx/DFSC.xlsx
@@ -2683,10 +2683,10 @@
         <v>0.017795</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.384239</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>1.045409</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -13702,7 +13702,11 @@
           <t>Deferred tax recovery 22</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -15422,7 +15426,11 @@
           <t>Deferred tax recovery 21</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
